--- a/resources/reselling/files/reselling-adv-ceiling.xlsx
+++ b/resources/reselling/files/reselling-adv-ceiling.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,11 +68,6 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -162,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,8 +201,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,10 +566,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="59" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -629,7 +622,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Average net per item (after fees, postage, packing, cost)</t>
+          <t>Average net per item (after fees, shipping, packing, cost)</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -977,10 +970,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/resources/reselling/files/reselling-adv-ceiling.xlsx
+++ b/resources/reselling/files/reselling-adv-ceiling.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,10 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -157,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +205,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -967,9 +972,13 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
